--- a/engine/adnocdrill_study/ADNOCDRILL_Valuation_Model_09082026.xlsx
+++ b/engine/adnocdrill_study/ADNOCDRILL_Valuation_Model_09082026.xlsx
@@ -2992,102 +2992,102 @@
     </row>
     <row r="6">
       <c r="A6" s="30" t="n">
-        <v>0.064621</v>
+        <v>0.070509</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>6.439473892704435</v>
+        <v>5.769166086163977</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>6.828836475852107</v>
+        <v>6.062699876390865</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>7.303575178495154</v>
+        <v>6.412729861015036</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>7.896012299223474</v>
+        <v>6.837877475707652</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>8.657142213453122</v>
+        <v>7.365957883791108</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="30" t="n">
-        <v>0.069621</v>
+        <v>0.07550900000000001</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>5.86179219004092</v>
+        <v>5.294433301743014</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>6.167691868302923</v>
+        <v>5.528915757954008</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>6.533583992603078</v>
+        <v>5.804201257221636</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>6.979635898737802</v>
+        <v>6.132407355740817</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>7.53619504708212</v>
+        <v>6.530976954668978</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="30" t="n">
-        <v>0.07462100000000001</v>
+        <v>0.080509</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>5.373388977815597</v>
+        <v>4.8869298185536</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>5.617194738766592</v>
+        <v>5.076403732773973</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>5.904167753049582</v>
+        <v>5.295900983486154</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>6.247357108751856</v>
+        <v>5.553534670320419</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>6.665660749023269</v>
+        <v>5.860630429140301</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="30" t="n">
-        <v>0.079621</v>
+        <v>0.085509</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>4.955035063878917</v>
+        <v>4.53330570271436</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>5.151671126876438</v>
+        <v>4.687882638175869</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>5.379973582807436</v>
+        <v>4.864891506686237</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>5.648638645472497</v>
+        <v>5.069893117310771</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>5.969867582500469</v>
+        <v>5.310451849370167</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="30" t="n">
-        <v>0.084621</v>
+        <v>0.09050900000000001</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>4.5926548285967</v>
+        <v>4.223527178768087</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>4.752822038737026</v>
+        <v>4.350648222464476</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>4.93658968054318</v>
+        <v>4.494741103123664</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>5.149895367859067</v>
+        <v>4.659691966991841</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>5.400850828456897</v>
+        <v>4.850671445679763</v>
       </c>
     </row>
     <row r="13">
@@ -3116,19 +3116,19 @@
     </row>
     <row r="15">
       <c r="B15" s="7" t="n">
-        <v>5.471874275925205</v>
+        <v>4.858397408763651</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>5.859638593805311</v>
+        <v>5.205966875502256</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.247402911685418</v>
+        <v>5.55353634224086</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>6.635167229565526</v>
+        <v>5.901105808979465</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>7.022931547445633</v>
+        <v>6.248675275718069</v>
       </c>
     </row>
     <row r="17">
@@ -3143,16 +3143,16 @@
         <v>0.5</v>
       </c>
       <c r="C18" s="32" t="n">
-        <v>0.6</v>
+        <v>0.664</v>
       </c>
       <c r="D18" s="32" t="n">
-        <v>0.664</v>
+        <v>0.795</v>
       </c>
       <c r="E18" s="32" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F18" s="32" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="19">
@@ -3160,16 +3160,16 @@
         <v>7.387409647763772</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>6.649660356490521</v>
+        <v>6.247402911685418</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>6.247402911685418</v>
+        <v>5.55353634224086</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>5.52994449165278</v>
+        <v>5.094898154178789</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>4.719959938114322</v>
+        <v>4.685293656086891</v>
       </c>
     </row>
   </sheetData>
@@ -4458,10 +4458,10 @@
         <v/>
       </c>
       <c r="D4" s="7" t="n">
-        <v>5.648676479469689</v>
+        <v>5.069894525638941</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>6.979692495465288</v>
+        <v>6.132409373287555</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -4484,10 +4484,10 @@
         <v/>
       </c>
       <c r="D5" s="7" t="n">
-        <v>4.954797022996693</v>
+        <v>4.515000834928367</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>5.917443513705311</v>
+        <v>5.312300636475432</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -4536,10 +4536,10 @@
         <v/>
       </c>
       <c r="D7" s="7" t="n">
-        <v>5.847218426942332</v>
+        <v>5.25805921254539</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>7.092982609192152</v>
+        <v>6.24425658344284</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -4562,10 +4562,10 @@
         <v/>
       </c>
       <c r="D8" s="7" t="n">
-        <v>5.243458168375043</v>
+        <v>4.734724445330244</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>5.897755596954919</v>
+        <v>5.330209782897206</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -4833,11 +4833,11 @@
         </is>
       </c>
       <c r="C12" s="18" t="n">
-        <v>0.664</v>
+        <v>0.795</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Own-stock 5-year weekly regression against an equal-weight ADX composite built from the full committed 18-name UAE price library; n=249 weekly observations, R-squared 0.160, standard error 0.097, 90% interval 0.50 to 0.82. Clears the regression usability gate (n&gt;=24, R-squared&gt;=5%, standard error below the absolute beta), so the first tier of the beta hierarchy applies and no peer beta is needed. Source: engine/adnocdrill_study/beta_reg.py</t>
+          <t>Own-stock 5-year weekly regression against the FTSE ADX General Index — the headline index of the exchange the stock actually trades on, held at engine/raw_indices/AE/ADXGENERAL.csv (3,884 sessions, 02-Jan-2011 to 24-Jul-2026, screened for blanks, duplicate dates, limit-exceeding single-session moves and trading-day density before use). n=247 weekly observations, R-squared 0.128, standard error 0.133, 90% interval 0.58 to 1.01. Clears the regression usability gate (n&gt;=24, R-squared&gt;=5%, standard error below the absolute beta), so the first tier of the beta hierarchy applies and no peer beta is needed. SUPERSEDES a prior 0.664 measured against an equal-weight composite of the 18-name UAE price library; that composite under-weights the large-capitalisation names the published index is concentrated in, and it is retained as a robustness check rather than as the regressor. The index series ends 24-Jul-2026 against a 07-Aug-2026 price anchor, a 14-day gap that costs the regression two of roughly 250 weekly observations. Source: engine/adnocdrill_study/beta_reg.py</t>
         </is>
       </c>
     </row>

--- a/engine/adnocdrill_study/ADNOCDRILL_Valuation_Model_09082026.xlsx
+++ b/engine/adnocdrill_study/ADNOCDRILL_Valuation_Model_09082026.xlsx
@@ -3485,102 +3485,102 @@
     </row>
     <row r="6">
       <c r="A6" s="30" t="n">
-        <v>0.070088</v>
+        <v>0.070017</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>6.419490700694</v>
+        <v>6.42766391695358</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>6.759316563720758</v>
+        <v>6.768601659624352</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>7.165131031764513</v>
+        <v>7.175843424242394</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>7.658887375656863</v>
+        <v>7.671482205214462</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>8.27349140605758</v>
+        <v>8.28865280138381</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="30" t="n">
-        <v>0.075088</v>
+        <v>0.075017</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>5.888680380964527</v>
+        <v>5.895647484380923</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>6.160485109709473</v>
+        <v>6.168291993031424</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>6.479976393087424</v>
+        <v>6.488836744244655</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>6.861435063223742</v>
+        <v>6.871646926625301</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>7.325476600986408</v>
+        <v>7.337469846024741</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="30" t="n">
-        <v>0.08008800000000001</v>
+        <v>0.080017</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>5.433471210355845</v>
+        <v>5.439481047305022</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>5.653418317899793</v>
+        <v>5.660074434571938</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>5.908484966078198</v>
+        <v>5.915936151837309</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>6.208233911017926</v>
+        <v>6.216681862441138</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>6.5660462909441</v>
+        <v>6.575772187773681</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="30" t="n">
-        <v>0.085088</v>
+        <v>0.085017</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>5.038765575677691</v>
+        <v>5.04400294830865</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>5.218484767267036</v>
+        <v>5.224227510587604</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>5.424473297701325</v>
+        <v>5.430827431654345</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>5.663288883707259</v>
+        <v>5.670394683480425</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>5.943870056971861</v>
+        <v>5.951917578067409</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="30" t="n">
-        <v>0.090088</v>
+        <v>0.090017</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>4.693235930222037</v>
+        <v>4.697840949216351</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>4.841281667522331</v>
+        <v>4.846287335229237</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>5.009229145385788</v>
+        <v>5.014712506263988</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>5.201664863757824</v>
+        <v>5.207725745666933</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>5.424701916894012</v>
+        <v>5.431472329368608</v>
       </c>
     </row>
     <row r="13">
@@ -3609,19 +3609,19 @@
     </row>
     <row r="15">
       <c r="B15" s="7" t="n">
-        <v>5.448410285980434</v>
+        <v>5.455912014219901</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>5.828342898127153</v>
+        <v>5.836310793709535</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.208275510273871</v>
+        <v>6.216709573199168</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>6.58820812242059</v>
+        <v>6.597108352688803</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>6.968140734567308</v>
+        <v>6.977507132178437</v>
       </c>
     </row>
     <row r="17">
@@ -3650,19 +3650,19 @@
     </row>
     <row r="19">
       <c r="B19" s="7" t="n">
-        <v>8.247174215577701</v>
+        <v>8.255947841213244</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>6.980409976410579</v>
+        <v>6.989098049811913</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>6.208275510273871</v>
+        <v>6.216709573199168</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>5.697448890512884</v>
+        <v>5.705631284265208</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>5.240935740393224</v>
+        <v>5.248837151276451</v>
       </c>
     </row>
   </sheetData>
@@ -4951,10 +4951,10 @@
         <v/>
       </c>
       <c r="D4" s="7" t="n">
-        <v>5.663323877713519</v>
+        <v>5.670417989227845</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>6.861485341840793</v>
+        <v>6.871680427664845</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         <v/>
       </c>
       <c r="D5" s="7" t="n">
-        <v>4.987475889000974</v>
+        <v>4.99287555193404</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>5.874258605493419</v>
+        <v>5.881592684613398</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -5055,10 +5055,10 @@
         <v/>
       </c>
       <c r="D8" s="7" t="n">
-        <v>3.229876783026447</v>
+        <v>3.233098840320228</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>3.695757828474163</v>
+        <v>3.699392584601869</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -5196,11 +5196,11 @@
         </is>
       </c>
       <c r="C5" s="17" t="n">
-        <v>5.94</v>
+        <v>5.8</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Uploaded ADX daily price history for ADNOCDRILL, last close 07-Aug-2026</t>
+          <t>Uploaded ADX daily price history for ADNOCDRILL, last close 03-Sep-2026 — the latest price supplied to this repository (SUPPLIED_03-09-2026.json). Superseded: AED 5.94 of 7 August 2026, on which every edition before this one was struck</t>
         </is>
       </c>
     </row>
